--- a/United Spirits Excel.xlsx
+++ b/United Spirits Excel.xlsx
@@ -47,7 +47,7 @@
     <numFmt numFmtId="178" formatCode="0.000000_);\(0.000000\)"/>
     <numFmt numFmtId="179" formatCode="0_);\(0\)"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -254,6 +254,9 @@
       <color theme="1" tint="0.3499862666707358"/>
       <sz val="10"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -914,7 +917,7 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="440">
+  <cellXfs count="441">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1513,6 +1516,7 @@
     <xf numFmtId="175" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2429,7 +2433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N28"/>
+  <dimension ref="B2:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="17.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -3298,6 +3302,239 @@
       <c r="N28" t="inlineStr">
         <is>
           <t>FY26 actual: Other expenses Rs1,577cr / NSV Rs12,467cr = 12.65% (consolidated); held flat absent explicit guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="440" t="inlineStr">
+        <is>
+          <t>Revenue Build-Up: P&amp;A Growth Algorithm (Volume vs Price/Mix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Volume/Mix growth % (P&amp;A)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Mgmt algo, repeated Q2-Q4 FY26 concalls: '4% to 5% volume/mix'. Midpoint 4.5%. (Praveen Someshwar, MD&amp;CEO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Price/Mix growth % (P&amp;A)</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Mgmt algo: '6% to 8% price/mix'. Midpoint 7%. Together imply double-digit P&amp;A NSV growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Implied P&amp;A NSV growth % (memo)</t>
+        </is>
+      </c>
+      <c r="E33">
+        <f>(1+E31)*(1+E32)-1</f>
+        <v/>
+      </c>
+      <c r="F33">
+        <f>(1+F31)*(1+F32)-1</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>(1+G31)*(1+G32)-1</f>
+        <v/>
+      </c>
+      <c r="H33">
+        <f>(1+H31)*(1+H32)-1</f>
+        <v/>
+      </c>
+      <c r="I33">
+        <f>(1+I31)*(1+I32)-1</f>
+        <v/>
+      </c>
+      <c r="J33">
+        <f>(1+J31)*(1+J32)-1</f>
+        <v/>
+      </c>
+      <c r="K33">
+        <f>(1+K31)*(1+K32)-1</f>
+        <v/>
+      </c>
+      <c r="L33">
+        <f>(1+L31)*(1+L32)-1</f>
+        <v/>
+      </c>
+      <c r="N33">
+        <f> (1+vol)*(1+price/mix)-1. ~11.8% - management's 'strong double-digit' P&amp;A guidance</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Blended NSV growth used (Scenarios, base)</t>
+        </is>
+      </c>
+      <c r="E34">
+        <f>Scenarios!H10</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>Scenarios!I10</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>Scenarios!J10</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>Scenarios!K10</f>
+        <v/>
+      </c>
+      <c r="I34">
+        <f>Scenarios!L10</f>
+        <v/>
+      </c>
+      <c r="J34">
+        <f>Scenarios!M10</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>Scenarios!N10</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>Scenarios!O10</f>
+        <v/>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Reconciliation: blended growth (~9% FY27 fading to 6.5%) is BELOW the pure P&amp;A algo because it absorbs the declining Popular segment (~9% of NSV) and FY27 Maharashtra/AP state headwinds. Gap is intentional/conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="440" t="inlineStr">
+        <is>
+          <t>Management Guidance Flags (Memo - qualify base case; not double-counted in P&amp;L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>India-UK FTA benefit (Rs cr, annualised)</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>115</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Q3 FY26 concall: 'INR110 crores to INR120 crores' annualised bulk-scotch duty benefit (Pradeep Jain). Flows ~Q2 FY27; mgmt says this is 'on top of' the BAU double-digit guidance, so it is UPSIDE not in base case</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FY27 packaging cost headwind (% of GM, H1)</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Q4 FY26 concall: packaging (~1/3 of COGS) inflating 4-5% above run-rate; '1.25% to 1.5%' GM hit (~Rs35-40cr) in Apr-Jun; 'could become 2x to 2.5x' next qtr. Partly explains the FY27 GM dip to 45.5% in Scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Productivity savings run-rate (Rs cr)</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>415</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Q4 FY26 concall: underlying productivity Rs340-350cr (FY24, ex mono-carton one-off) -&gt; Rs388cr (FY25) -&gt; Rs415cr (FY26); multi-year supply-agility programme ~3-3.5 yrs in. Offsets &gt;80% of input inflation - embedded in the gross-margin ramp</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EBITDA margin ceiling (mgmt 'high teens')</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Q2 FY26 concall: 'we have reached... mid-to-high teens... sustain at the high-teens level' (Pradeep Jain). GUARDRAIL: model's terminal EBITDA margin (~20.25% by FY30 in Ratio Analysis) exceeds this - review/cap recommended</t>
         </is>
       </c>
     </row>

--- a/United Spirits Excel.xlsx
+++ b/United Spirits Excel.xlsx
@@ -7,20 +7,21 @@
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PPT Sheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Valuation Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="DCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ratio Analysis" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="PL" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CS" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Assumptions" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Working Capital Schedule" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Working Schedules" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Beta Calculation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Company &amp; Market Insights" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Notes to accounts" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Revenue Drivers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PPT Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Valuation Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DCF" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Ratio Analysis" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PL" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="BS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="CS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Working Capital Schedule" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Working Schedules" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Beta Calculation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Company &amp; Market Insights" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Notes to accounts" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -47,7 +48,7 @@
     <numFmt numFmtId="178" formatCode="0.000000_);\(0.000000\)"/>
     <numFmt numFmtId="179" formatCode="0_);\(0\)"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -258,8 +259,16 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -300,6 +309,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -917,7 +931,7 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="441">
+  <cellXfs count="445">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1517,6 +1531,10 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2018,6 +2036,13 @@
       <c r="J4" s="1" t="n"/>
       <c r="K4" s="1" t="n"/>
     </row>
+    <row r="6">
+      <c r="C6" s="444" t="inlineStr">
+        <is>
+          <t>NOTE: 'Sales Growth %' below is now DRIVEN BY the 'Revenue Drivers' sheet (segment volume x price/mix build). Rows 12-14 (Base/Best/Bear blended) are retained for reference only; the live scenario logic sits in Revenue Drivers, toggled by the same switch in D4.</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="18" customHeight="1">
       <c r="I7" s="26" t="n"/>
     </row>
@@ -2070,35 +2095,35 @@
       <c r="F10" s="190" t="n"/>
       <c r="G10" s="190" t="n"/>
       <c r="H10" s="191">
-        <f>CHOOSE($D$4,H12,H13,H14)</f>
+        <f>'Revenue Drivers'!E32</f>
         <v/>
       </c>
       <c r="I10" s="191">
-        <f>CHOOSE($D$4,I12,I13,I14)</f>
+        <f>'Revenue Drivers'!F32</f>
         <v/>
       </c>
       <c r="J10" s="191">
-        <f>CHOOSE($D$4,J12,J13,J14)</f>
+        <f>'Revenue Drivers'!G32</f>
         <v/>
       </c>
       <c r="K10" s="191">
-        <f>CHOOSE($D$4,K12,K13,K14)</f>
+        <f>'Revenue Drivers'!H32</f>
         <v/>
       </c>
       <c r="L10" s="191">
-        <f>CHOOSE($D$4,L12,L13,L14)</f>
+        <f>'Revenue Drivers'!I32</f>
         <v/>
       </c>
       <c r="M10" s="191">
-        <f>CHOOSE($D$4,M12,M13,M14)</f>
+        <f>'Revenue Drivers'!J32</f>
         <v/>
       </c>
       <c r="N10" s="191">
-        <f>CHOOSE($D$4,N12,N13,N14)</f>
+        <f>'Revenue Drivers'!K32</f>
         <v/>
       </c>
       <c r="O10" s="192">
-        <f>CHOOSE($D$4,O12,O13,O14)</f>
+        <f>'Revenue Drivers'!L32</f>
         <v/>
       </c>
       <c r="Q10" s="8" t="n"/>
@@ -2428,6 +2453,1388 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:T29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col width="2.77734375" customWidth="1" min="1" max="1"/>
+    <col width="50.77734375" customWidth="1" min="2" max="2"/>
+    <col width="10.77734375" customWidth="1" style="335" min="3" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1"/>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="45" t="inlineStr">
+        <is>
+          <t>Cash Flow Statement</t>
+        </is>
+      </c>
+      <c r="T2" s="246">
+        <f>BS!T2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Particulars</t>
+        </is>
+      </c>
+      <c r="C4" s="375" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D4" s="375">
+        <f>C4+1</f>
+        <v/>
+      </c>
+      <c r="E4" s="375">
+        <f>D4+1</f>
+        <v/>
+      </c>
+      <c r="F4" s="375">
+        <f>E4+1</f>
+        <v/>
+      </c>
+      <c r="G4" s="375">
+        <f>F4+1</f>
+        <v/>
+      </c>
+      <c r="H4" s="375">
+        <f>G4+1</f>
+        <v/>
+      </c>
+      <c r="I4" s="375">
+        <f>H4+1</f>
+        <v/>
+      </c>
+      <c r="J4" s="375">
+        <f>I4+1</f>
+        <v/>
+      </c>
+      <c r="K4" s="375">
+        <f>J4+1</f>
+        <v/>
+      </c>
+      <c r="L4" s="375">
+        <f>K4+1</f>
+        <v/>
+      </c>
+      <c r="M4" s="376">
+        <f>L4+1</f>
+        <v/>
+      </c>
+      <c r="N4" s="376">
+        <f>M4+1</f>
+        <v/>
+      </c>
+      <c r="O4" s="376">
+        <f>N4+1</f>
+        <v/>
+      </c>
+      <c r="P4" s="376">
+        <f>O4+1</f>
+        <v/>
+      </c>
+      <c r="Q4" s="376">
+        <f>P4+1</f>
+        <v/>
+      </c>
+      <c r="R4" s="376">
+        <f>Q4+1</f>
+        <v/>
+      </c>
+      <c r="S4" s="376">
+        <f>R4+1</f>
+        <v/>
+      </c>
+      <c r="T4" s="376">
+        <f>S4+1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1"/>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Net Profit Aafter Tax (PAT)</t>
+        </is>
+      </c>
+      <c r="C6" s="388">
+        <f>PL!C22</f>
+        <v/>
+      </c>
+      <c r="D6" s="388">
+        <f>PL!D22</f>
+        <v/>
+      </c>
+      <c r="E6" s="388">
+        <f>PL!E22</f>
+        <v/>
+      </c>
+      <c r="F6" s="388">
+        <f>PL!F22</f>
+        <v/>
+      </c>
+      <c r="G6" s="388">
+        <f>PL!G22</f>
+        <v/>
+      </c>
+      <c r="H6" s="388">
+        <f>PL!H22</f>
+        <v/>
+      </c>
+      <c r="I6" s="388">
+        <f>PL!I22</f>
+        <v/>
+      </c>
+      <c r="J6" s="388">
+        <f>PL!J22</f>
+        <v/>
+      </c>
+      <c r="K6" s="388">
+        <f>PL!K22</f>
+        <v/>
+      </c>
+      <c r="L6" s="388">
+        <f>PL!L22</f>
+        <v/>
+      </c>
+      <c r="M6" s="388">
+        <f>PL!M22</f>
+        <v/>
+      </c>
+      <c r="N6" s="388">
+        <f>PL!N22</f>
+        <v/>
+      </c>
+      <c r="O6" s="388">
+        <f>PL!O22</f>
+        <v/>
+      </c>
+      <c r="P6" s="388">
+        <f>PL!P22</f>
+        <v/>
+      </c>
+      <c r="Q6" s="388">
+        <f>PL!Q22</f>
+        <v/>
+      </c>
+      <c r="R6" s="388">
+        <f>PL!R22</f>
+        <v/>
+      </c>
+      <c r="S6" s="388">
+        <f>PL!S22</f>
+        <v/>
+      </c>
+      <c r="T6" s="388">
+        <f>PL!T22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="C7" s="353">
+        <f>-PL!C13</f>
+        <v/>
+      </c>
+      <c r="D7" s="353">
+        <f>-PL!D13</f>
+        <v/>
+      </c>
+      <c r="E7" s="353">
+        <f>-PL!E13</f>
+        <v/>
+      </c>
+      <c r="F7" s="353">
+        <f>-PL!F13</f>
+        <v/>
+      </c>
+      <c r="G7" s="353">
+        <f>-PL!G13</f>
+        <v/>
+      </c>
+      <c r="H7" s="353">
+        <f>-PL!H13</f>
+        <v/>
+      </c>
+      <c r="I7" s="353">
+        <f>-PL!I13</f>
+        <v/>
+      </c>
+      <c r="J7" s="353">
+        <f>-PL!J13</f>
+        <v/>
+      </c>
+      <c r="K7" s="353">
+        <f>-PL!K13</f>
+        <v/>
+      </c>
+      <c r="L7" s="353">
+        <f>-PL!L13</f>
+        <v/>
+      </c>
+      <c r="M7" s="353">
+        <f>-PL!M13</f>
+        <v/>
+      </c>
+      <c r="N7" s="353">
+        <f>-PL!N13</f>
+        <v/>
+      </c>
+      <c r="O7" s="353">
+        <f>-PL!O13</f>
+        <v/>
+      </c>
+      <c r="P7" s="353">
+        <f>-PL!P13</f>
+        <v/>
+      </c>
+      <c r="Q7" s="353">
+        <f>-PL!Q13</f>
+        <v/>
+      </c>
+      <c r="R7" s="353">
+        <f>-PL!R13</f>
+        <v/>
+      </c>
+      <c r="S7" s="353">
+        <f>-PL!S13</f>
+        <v/>
+      </c>
+      <c r="T7" s="353">
+        <f>-PL!T13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="B8" s="96" t="inlineStr">
+        <is>
+          <t>+/- in other non cash items</t>
+        </is>
+      </c>
+      <c r="C8" s="380" t="n">
+        <v>227.2</v>
+      </c>
+      <c r="D8" s="380" t="n">
+        <v>358.900000000002</v>
+      </c>
+      <c r="E8" s="380" t="n">
+        <v>103.8999999999987</v>
+      </c>
+      <c r="F8" s="380" t="n">
+        <v>3.000000000000853</v>
+      </c>
+      <c r="G8" s="380" t="n">
+        <v>1752.2</v>
+      </c>
+      <c r="H8" s="380" t="n">
+        <v>611.5000000000007</v>
+      </c>
+      <c r="I8" s="380" t="n">
+        <v>-468.8000000000003</v>
+      </c>
+      <c r="J8" s="380" t="n">
+        <v>-431.8999999999996</v>
+      </c>
+      <c r="K8" s="380" t="n">
+        <v>94.59999999999991</v>
+      </c>
+      <c r="L8" s="380" t="n">
+        <v>-37</v>
+      </c>
+      <c r="M8" s="335">
+        <f>-PL!M18-PL!M17</f>
+        <v/>
+      </c>
+      <c r="N8" s="335">
+        <f>-PL!N18-PL!N17</f>
+        <v/>
+      </c>
+      <c r="O8" s="335">
+        <f>-PL!O18-PL!O17</f>
+        <v/>
+      </c>
+      <c r="P8" s="335">
+        <f>-PL!P18-PL!P17</f>
+        <v/>
+      </c>
+      <c r="Q8" s="335">
+        <f>-PL!Q18-PL!Q17</f>
+        <v/>
+      </c>
+      <c r="R8" s="335">
+        <f>-PL!R18-PL!R17</f>
+        <v/>
+      </c>
+      <c r="S8" s="335">
+        <f>-PL!S18-PL!S17</f>
+        <v/>
+      </c>
+      <c r="T8" s="335">
+        <f>-PL!T18-PL!T17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="153" t="inlineStr">
+        <is>
+          <t>+/- change in NWC</t>
+        </is>
+      </c>
+      <c r="C9" s="389" t="n">
+        <v>138</v>
+      </c>
+      <c r="D9" s="390">
+        <f>-'Working Capital Schedule'!D21</f>
+        <v/>
+      </c>
+      <c r="E9" s="390">
+        <f>-'Working Capital Schedule'!E21</f>
+        <v/>
+      </c>
+      <c r="F9" s="390">
+        <f>-'Working Capital Schedule'!F21</f>
+        <v/>
+      </c>
+      <c r="G9" s="390">
+        <f>-'Working Capital Schedule'!G21</f>
+        <v/>
+      </c>
+      <c r="H9" s="390">
+        <f>-'Working Capital Schedule'!H21</f>
+        <v/>
+      </c>
+      <c r="I9" s="390">
+        <f>-'Working Capital Schedule'!I21</f>
+        <v/>
+      </c>
+      <c r="J9" s="390">
+        <f>-'Working Capital Schedule'!J21</f>
+        <v/>
+      </c>
+      <c r="K9" s="390">
+        <f>-'Working Capital Schedule'!K21</f>
+        <v/>
+      </c>
+      <c r="L9" s="390">
+        <f>-'Working Capital Schedule'!L21</f>
+        <v/>
+      </c>
+      <c r="M9" s="390">
+        <f>-'Working Capital Schedule'!M21</f>
+        <v/>
+      </c>
+      <c r="N9" s="390">
+        <f>-'Working Capital Schedule'!N21</f>
+        <v/>
+      </c>
+      <c r="O9" s="390">
+        <f>-'Working Capital Schedule'!O21</f>
+        <v/>
+      </c>
+      <c r="P9" s="390">
+        <f>-'Working Capital Schedule'!P21</f>
+        <v/>
+      </c>
+      <c r="Q9" s="390">
+        <f>-'Working Capital Schedule'!Q21</f>
+        <v/>
+      </c>
+      <c r="R9" s="390">
+        <f>-'Working Capital Schedule'!R21</f>
+        <v/>
+      </c>
+      <c r="S9" s="390">
+        <f>-'Working Capital Schedule'!S21</f>
+        <v/>
+      </c>
+      <c r="T9" s="390">
+        <f>-'Working Capital Schedule'!T21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Cash flow from Operating Activities</t>
+        </is>
+      </c>
+      <c r="C10" s="355">
+        <f>SUM(C6:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="355">
+        <f>SUM(D6:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="355">
+        <f>SUM(E6:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="355">
+        <f>SUM(F6:F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="355">
+        <f>SUM(G6:G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="355">
+        <f>SUM(H6:H9)</f>
+        <v/>
+      </c>
+      <c r="I10" s="355">
+        <f>SUM(I6:I9)</f>
+        <v/>
+      </c>
+      <c r="J10" s="355">
+        <f>SUM(J6:J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="355">
+        <f>SUM(K6:K9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="355">
+        <f>SUM(L6:L9)</f>
+        <v/>
+      </c>
+      <c r="M10" s="355">
+        <f>SUM(M6:M9)</f>
+        <v/>
+      </c>
+      <c r="N10" s="355">
+        <f>SUM(N6:N9)</f>
+        <v/>
+      </c>
+      <c r="O10" s="355">
+        <f>SUM(O6:O9)</f>
+        <v/>
+      </c>
+      <c r="P10" s="355">
+        <f>SUM(P6:P9)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="355">
+        <f>SUM(Q6:Q9)</f>
+        <v/>
+      </c>
+      <c r="R10" s="355">
+        <f>SUM(R6:R9)</f>
+        <v/>
+      </c>
+      <c r="S10" s="355">
+        <f>SUM(S6:S9)</f>
+        <v/>
+      </c>
+      <c r="T10" s="355">
+        <f>SUM(T6:T9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Interest Received</t>
+        </is>
+      </c>
+      <c r="C11" s="335" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D11" s="335" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E11" s="335" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F11" s="335" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G11" s="335" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H11" s="335" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I11" s="335" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J11" s="335" t="n">
+        <v>42</v>
+      </c>
+      <c r="K11" s="335" t="n">
+        <v>36</v>
+      </c>
+      <c r="L11" s="335" t="n">
+        <v>67</v>
+      </c>
+      <c r="M11" s="335">
+        <f>M21*Assumptions!E9</f>
+        <v/>
+      </c>
+      <c r="N11" s="335">
+        <f>N21*Assumptions!F9</f>
+        <v/>
+      </c>
+      <c r="O11" s="335">
+        <f>O21*Assumptions!G9</f>
+        <v/>
+      </c>
+      <c r="P11" s="335">
+        <f>P21*Assumptions!H9</f>
+        <v/>
+      </c>
+      <c r="Q11" s="335">
+        <f>Q21*Assumptions!I9</f>
+        <v/>
+      </c>
+      <c r="R11" s="335">
+        <f>R21*Assumptions!J9</f>
+        <v/>
+      </c>
+      <c r="S11" s="335">
+        <f>S21*Assumptions!K9</f>
+        <v/>
+      </c>
+      <c r="T11" s="335">
+        <f>T21*Assumptions!L9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="C12" s="335" t="n">
+        <v>-311</v>
+      </c>
+      <c r="D12" s="335" t="n">
+        <v>-184.3</v>
+      </c>
+      <c r="E12" s="335" t="n">
+        <v>-173</v>
+      </c>
+      <c r="F12" s="335" t="n">
+        <v>-211.6</v>
+      </c>
+      <c r="G12" s="335" t="n">
+        <v>-158.9</v>
+      </c>
+      <c r="H12" s="335" t="n">
+        <v>-134</v>
+      </c>
+      <c r="I12" s="335" t="n">
+        <v>-136.6</v>
+      </c>
+      <c r="J12" s="335" t="n">
+        <v>-98</v>
+      </c>
+      <c r="K12" s="335" t="n">
+        <v>-162</v>
+      </c>
+      <c r="L12" s="335" t="n">
+        <v>-181</v>
+      </c>
+      <c r="M12" s="335">
+        <f>-'Working Schedules'!H42</f>
+        <v/>
+      </c>
+      <c r="N12" s="335">
+        <f>-'Working Schedules'!I42</f>
+        <v/>
+      </c>
+      <c r="O12" s="335">
+        <f>-'Working Schedules'!J42</f>
+        <v/>
+      </c>
+      <c r="P12" s="335">
+        <f>-'Working Schedules'!K42</f>
+        <v/>
+      </c>
+      <c r="Q12" s="335">
+        <f>-'Working Schedules'!L42</f>
+        <v/>
+      </c>
+      <c r="R12" s="335">
+        <f>-'Working Schedules'!M42</f>
+        <v/>
+      </c>
+      <c r="S12" s="335">
+        <f>-'Working Schedules'!N42</f>
+        <v/>
+      </c>
+      <c r="T12" s="335">
+        <f>-'Working Schedules'!O42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="151" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="C13" s="391" t="n">
+        <v>64</v>
+      </c>
+      <c r="D13" s="391" t="n">
+        <v>284</v>
+      </c>
+      <c r="E13" s="391" t="n">
+        <v>128</v>
+      </c>
+      <c r="F13" s="391" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" s="391" t="n">
+        <v>35</v>
+      </c>
+      <c r="H13" s="391" t="n">
+        <v>-176</v>
+      </c>
+      <c r="I13" s="391" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" s="391" t="n">
+        <v>-262</v>
+      </c>
+      <c r="K13" s="391" t="n">
+        <v>-227</v>
+      </c>
+      <c r="L13" s="391" t="n">
+        <v>75</v>
+      </c>
+      <c r="M13" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="391" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>Cash flow from investing activities</t>
+        </is>
+      </c>
+      <c r="C14" s="355">
+        <f>SUM(C11:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="355">
+        <f>SUM(D11:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="355">
+        <f>SUM(E11:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="355">
+        <f>SUM(F11:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="355">
+        <f>SUM(G11:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="355">
+        <f>SUM(H11:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="355">
+        <f>SUM(I11:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="355">
+        <f>SUM(J11:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="355">
+        <f>SUM(K11:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="355">
+        <f>SUM(L11:L13)</f>
+        <v/>
+      </c>
+      <c r="M14" s="355">
+        <f>SUM(M11:M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="355">
+        <f>SUM(N11:N13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="355">
+        <f>SUM(O11:O13)</f>
+        <v/>
+      </c>
+      <c r="P14" s="355">
+        <f>SUM(P11:P13)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="355">
+        <f>SUM(Q11:Q13)</f>
+        <v/>
+      </c>
+      <c r="R14" s="355">
+        <f>SUM(R11:R13)</f>
+        <v/>
+      </c>
+      <c r="S14" s="355">
+        <f>SUM(S11:S13)</f>
+        <v/>
+      </c>
+      <c r="T14" s="355">
+        <f>SUM(T11:T13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Repayment Lease Liabilities</t>
+        </is>
+      </c>
+      <c r="C15" s="335" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="D15" s="335" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="335" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="335" t="n">
+        <v>-64.5</v>
+      </c>
+      <c r="G15" s="335" t="n">
+        <v>-80.7</v>
+      </c>
+      <c r="H15" s="335" t="n">
+        <v>-100.2</v>
+      </c>
+      <c r="I15" s="335" t="n">
+        <v>-124</v>
+      </c>
+      <c r="J15" s="335" t="n">
+        <v>-126</v>
+      </c>
+      <c r="K15" s="335" t="n">
+        <v>-137</v>
+      </c>
+      <c r="L15" s="335" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M15" s="335">
+        <f>'Working Schedules'!H9</f>
+        <v/>
+      </c>
+      <c r="N15" s="335">
+        <f>'Working Schedules'!I9</f>
+        <v/>
+      </c>
+      <c r="O15" s="335">
+        <f>'Working Schedules'!J9</f>
+        <v/>
+      </c>
+      <c r="P15" s="335">
+        <f>'Working Schedules'!K9</f>
+        <v/>
+      </c>
+      <c r="Q15" s="335">
+        <f>'Working Schedules'!L9</f>
+        <v/>
+      </c>
+      <c r="R15" s="335">
+        <f>'Working Schedules'!M9</f>
+        <v/>
+      </c>
+      <c r="S15" s="335">
+        <f>'Working Schedules'!N9</f>
+        <v/>
+      </c>
+      <c r="T15" s="335">
+        <f>'Working Schedules'!O9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Interest Paid</t>
+        </is>
+      </c>
+      <c r="C16" s="335" t="n">
+        <v>-375.2</v>
+      </c>
+      <c r="D16" s="335" t="n">
+        <v>-252.8</v>
+      </c>
+      <c r="E16" s="335" t="n">
+        <v>-229.3</v>
+      </c>
+      <c r="F16" s="335" t="n">
+        <v>-181.1</v>
+      </c>
+      <c r="G16" s="335" t="n">
+        <v>-142</v>
+      </c>
+      <c r="H16" s="335" t="n">
+        <v>-50.1</v>
+      </c>
+      <c r="I16" s="335" t="n">
+        <v>-36.3</v>
+      </c>
+      <c r="J16" s="335" t="n">
+        <v>-21</v>
+      </c>
+      <c r="K16" s="335" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L16" s="335" t="n">
+        <v>-37</v>
+      </c>
+      <c r="M16" s="335">
+        <f>PL!M17</f>
+        <v/>
+      </c>
+      <c r="N16" s="335">
+        <f>PL!N17</f>
+        <v/>
+      </c>
+      <c r="O16" s="335">
+        <f>PL!O17</f>
+        <v/>
+      </c>
+      <c r="P16" s="335">
+        <f>PL!P17</f>
+        <v/>
+      </c>
+      <c r="Q16" s="335">
+        <f>PL!Q17</f>
+        <v/>
+      </c>
+      <c r="R16" s="335">
+        <f>PL!R17</f>
+        <v/>
+      </c>
+      <c r="S16" s="335">
+        <f>PL!S17</f>
+        <v/>
+      </c>
+      <c r="T16" s="335">
+        <f>PL!T17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dividend Paid</t>
+        </is>
+      </c>
+      <c r="C17" s="335" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="335" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="335" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="335" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="335" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="335" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="335" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="335" t="n">
+        <v>-284</v>
+      </c>
+      <c r="K17" s="335" t="n">
+        <v>-355</v>
+      </c>
+      <c r="L17" s="335" t="n">
+        <v>-1263</v>
+      </c>
+      <c r="M17" s="335">
+        <f>-Assumptions!E11*PL!M22</f>
+        <v/>
+      </c>
+      <c r="N17" s="335">
+        <f>-Assumptions!F11*PL!N22</f>
+        <v/>
+      </c>
+      <c r="O17" s="335">
+        <f>-Assumptions!G11*PL!O22</f>
+        <v/>
+      </c>
+      <c r="P17" s="335">
+        <f>-Assumptions!H11*PL!P22</f>
+        <v/>
+      </c>
+      <c r="Q17" s="335">
+        <f>-Assumptions!I11*PL!Q22</f>
+        <v/>
+      </c>
+      <c r="R17" s="335">
+        <f>-Assumptions!J11*PL!R22</f>
+        <v/>
+      </c>
+      <c r="S17" s="335">
+        <f>-Assumptions!K11*PL!S22</f>
+        <v/>
+      </c>
+      <c r="T17" s="335">
+        <f>-Assumptions!L11*PL!T22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="151" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+      <c r="C18" s="391" t="n">
+        <v>-86.40000000000001</v>
+      </c>
+      <c r="D18" s="391" t="n">
+        <v>-607.4</v>
+      </c>
+      <c r="E18" s="391" t="n">
+        <v>-653.6000000000003</v>
+      </c>
+      <c r="F18" s="391" t="n">
+        <v>-553.6</v>
+      </c>
+      <c r="G18" s="391" t="n">
+        <v>-1471.800000000001</v>
+      </c>
+      <c r="H18" s="391" t="n">
+        <v>-324.9</v>
+      </c>
+      <c r="I18" s="391" t="n">
+        <v>505.9</v>
+      </c>
+      <c r="J18" s="391" t="n">
+        <v>359.9</v>
+      </c>
+      <c r="K18" s="391" t="n">
+        <v>-27</v>
+      </c>
+      <c r="L18" s="391" t="n">
+        <v>255</v>
+      </c>
+      <c r="M18" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="391" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="391" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Cash flow from Financing activities</t>
+        </is>
+      </c>
+      <c r="C19" s="355">
+        <f>SUM(C15:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="355">
+        <f>SUM(D15:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="355">
+        <f>SUM(E15:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="355">
+        <f>SUM(F15:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="355">
+        <f>SUM(G15:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="355">
+        <f>SUM(H15:H18)</f>
+        <v/>
+      </c>
+      <c r="I19" s="355">
+        <f>SUM(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="355">
+        <f>SUM(J15:J18)</f>
+        <v/>
+      </c>
+      <c r="K19" s="355">
+        <f>SUM(K15:K18)</f>
+        <v/>
+      </c>
+      <c r="L19" s="355">
+        <f>SUM(L15:L18)</f>
+        <v/>
+      </c>
+      <c r="M19" s="355">
+        <f>SUM(M15:M18)</f>
+        <v/>
+      </c>
+      <c r="N19" s="355">
+        <f>SUM(N15:N18)</f>
+        <v/>
+      </c>
+      <c r="O19" s="355">
+        <f>SUM(O15:O18)</f>
+        <v/>
+      </c>
+      <c r="P19" s="355">
+        <f>SUM(P15:P18)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="355">
+        <f>SUM(Q15:Q18)</f>
+        <v/>
+      </c>
+      <c r="R19" s="355">
+        <f>SUM(R15:R18)</f>
+        <v/>
+      </c>
+      <c r="S19" s="355">
+        <f>SUM(S15:S18)</f>
+        <v/>
+      </c>
+      <c r="T19" s="355">
+        <f>SUM(T15:T18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>Net change in Cash</t>
+        </is>
+      </c>
+      <c r="C20" s="355">
+        <f>C10+C14+C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="355">
+        <f>D10+D14+D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="355">
+        <f>E10+E14+E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="355">
+        <f>F10+F14+F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="355">
+        <f>G10+G14+G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="355">
+        <f>H10+H14+H19</f>
+        <v/>
+      </c>
+      <c r="I20" s="355">
+        <f>I10+I14+I19</f>
+        <v/>
+      </c>
+      <c r="J20" s="355">
+        <f>J10+J14+J19</f>
+        <v/>
+      </c>
+      <c r="K20" s="355">
+        <f>K10+K14+K19</f>
+        <v/>
+      </c>
+      <c r="L20" s="355">
+        <f>L10+L14+L19</f>
+        <v/>
+      </c>
+      <c r="M20" s="355">
+        <f>M10+M14+M19</f>
+        <v/>
+      </c>
+      <c r="N20" s="355">
+        <f>N10+N14+N19</f>
+        <v/>
+      </c>
+      <c r="O20" s="355">
+        <f>O10+O14+O19</f>
+        <v/>
+      </c>
+      <c r="P20" s="355">
+        <f>P10+P14+P19</f>
+        <v/>
+      </c>
+      <c r="Q20" s="355">
+        <f>Q10+Q14+Q19</f>
+        <v/>
+      </c>
+      <c r="R20" s="355">
+        <f>R10+R14+R19</f>
+        <v/>
+      </c>
+      <c r="S20" s="355">
+        <f>S10+S14+S19</f>
+        <v/>
+      </c>
+      <c r="T20" s="355">
+        <f>T10+T14+T19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="151" t="inlineStr">
+        <is>
+          <t>Opening Cash Balance</t>
+        </is>
+      </c>
+      <c r="C21" s="389" t="n">
+        <v>138</v>
+      </c>
+      <c r="D21" s="390">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="E21" s="390">
+        <f>D22</f>
+        <v/>
+      </c>
+      <c r="F21" s="390">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="G21" s="390">
+        <f>F22</f>
+        <v/>
+      </c>
+      <c r="H21" s="390">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="I21" s="390">
+        <f>H22</f>
+        <v/>
+      </c>
+      <c r="J21" s="390">
+        <f>I22</f>
+        <v/>
+      </c>
+      <c r="K21" s="390">
+        <f>J22</f>
+        <v/>
+      </c>
+      <c r="L21" s="390">
+        <f>K22</f>
+        <v/>
+      </c>
+      <c r="M21" s="390">
+        <f>L22</f>
+        <v/>
+      </c>
+      <c r="N21" s="390">
+        <f>M22</f>
+        <v/>
+      </c>
+      <c r="O21" s="390">
+        <f>N22</f>
+        <v/>
+      </c>
+      <c r="P21" s="390">
+        <f>O22</f>
+        <v/>
+      </c>
+      <c r="Q21" s="390">
+        <f>P22</f>
+        <v/>
+      </c>
+      <c r="R21" s="390">
+        <f>Q22</f>
+        <v/>
+      </c>
+      <c r="S21" s="390">
+        <f>R22</f>
+        <v/>
+      </c>
+      <c r="T21" s="390">
+        <f>S22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Closing Cash Balance</t>
+        </is>
+      </c>
+      <c r="C22" s="355">
+        <f>C20+C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="355">
+        <f>D20+D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="355">
+        <f>E20+E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="355">
+        <f>F20+F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="355">
+        <f>G20+G21</f>
+        <v/>
+      </c>
+      <c r="H22" s="355">
+        <f>H20+H21</f>
+        <v/>
+      </c>
+      <c r="I22" s="355">
+        <f>I20+I21</f>
+        <v/>
+      </c>
+      <c r="J22" s="355">
+        <f>J20+J21</f>
+        <v/>
+      </c>
+      <c r="K22" s="355">
+        <f>K20+K21</f>
+        <v/>
+      </c>
+      <c r="L22" s="355">
+        <f>L20+L21</f>
+        <v/>
+      </c>
+      <c r="M22" s="355">
+        <f>M20+M21</f>
+        <v/>
+      </c>
+      <c r="N22" s="355">
+        <f>N20+N21</f>
+        <v/>
+      </c>
+      <c r="O22" s="355">
+        <f>O20+O21</f>
+        <v/>
+      </c>
+      <c r="P22" s="355">
+        <f>P20+P21</f>
+        <v/>
+      </c>
+      <c r="Q22" s="355">
+        <f>Q20+Q21</f>
+        <v/>
+      </c>
+      <c r="R22" s="355">
+        <f>R20+R21</f>
+        <v/>
+      </c>
+      <c r="S22" s="355">
+        <f>S20+S21</f>
+        <v/>
+      </c>
+      <c r="T22" s="355">
+        <f>T20+T21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="96" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="96" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3422,9 +4829,10 @@
         <f>(1+L31)*(1+L32)-1</f>
         <v/>
       </c>
-      <c r="N33">
-        <f> (1+vol)*(1+price/mix)-1. ~11.8% - management's 'strong double-digit' P&amp;A guidance</f>
-        <v/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Formula: (1+vol)*(1+price/mix)-1 = ~11.8%; management's 'strong double-digit' P&amp;A guidance</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -3543,7 +4951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4629,7 +6037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8169,7 +9577,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17783,7 +19191,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18584,7 +19992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19680,6 +21088,1325 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:L53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="440" t="inlineStr">
+        <is>
+          <t>United Spirits - Revenue Growth Drivers (Segment Build: Volume x Price/Mix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Scenario switch (shared with Scenarios!D4):</t>
+        </is>
+      </c>
+      <c r="F3" s="440">
+        <f>Scenarios!D4</f>
+        <v/>
+      </c>
+      <c r="G3" s="440">
+        <f>CHOOSE(Scenarios!D4,"BASE","BEST","BEAR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="440" t="inlineStr">
+        <is>
+          <t>Particulars</t>
+        </is>
+      </c>
+      <c r="D4" s="440" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E4" s="440">
+        <f>D4+1</f>
+        <v/>
+      </c>
+      <c r="F4" s="440">
+        <f>E4+1</f>
+        <v/>
+      </c>
+      <c r="G4" s="440">
+        <f>F4+1</f>
+        <v/>
+      </c>
+      <c r="H4" s="440">
+        <f>G4+1</f>
+        <v/>
+      </c>
+      <c r="I4" s="440">
+        <f>H4+1</f>
+        <v/>
+      </c>
+      <c r="J4" s="440">
+        <f>I4+1</f>
+        <v/>
+      </c>
+      <c r="K4" s="440">
+        <f>J4+1</f>
+        <v/>
+      </c>
+      <c r="L4" s="440">
+        <f>K4+1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="441" t="inlineStr">
+        <is>
+          <t>ACTIVE ASSUMPTIONS  (auto-selected by scenario switch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="440" t="inlineStr">
+        <is>
+          <t>P&amp;A volume growth %</t>
+        </is>
+      </c>
+      <c r="E7" s="382">
+        <f>CHOOSE(Scenarios!$D$4,E12,E13,E14)</f>
+        <v/>
+      </c>
+      <c r="F7" s="382">
+        <f>CHOOSE(Scenarios!$D$4,F12,F13,F14)</f>
+        <v/>
+      </c>
+      <c r="G7" s="382">
+        <f>CHOOSE(Scenarios!$D$4,G12,G13,G14)</f>
+        <v/>
+      </c>
+      <c r="H7" s="382">
+        <f>CHOOSE(Scenarios!$D$4,H12,H13,H14)</f>
+        <v/>
+      </c>
+      <c r="I7" s="382">
+        <f>CHOOSE(Scenarios!$D$4,I12,I13,I14)</f>
+        <v/>
+      </c>
+      <c r="J7" s="382">
+        <f>CHOOSE(Scenarios!$D$4,J12,J13,J14)</f>
+        <v/>
+      </c>
+      <c r="K7" s="382">
+        <f>CHOOSE(Scenarios!$D$4,K12,K13,K14)</f>
+        <v/>
+      </c>
+      <c r="L7" s="382">
+        <f>CHOOSE(Scenarios!$D$4,L12,L13,L14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="440" t="inlineStr">
+        <is>
+          <t>P&amp;A price/mix growth %</t>
+        </is>
+      </c>
+      <c r="E8" s="382">
+        <f>CHOOSE(Scenarios!$D$4,E16,E17,E18)</f>
+        <v/>
+      </c>
+      <c r="F8" s="382">
+        <f>CHOOSE(Scenarios!$D$4,F16,F17,F18)</f>
+        <v/>
+      </c>
+      <c r="G8" s="382">
+        <f>CHOOSE(Scenarios!$D$4,G16,G17,G18)</f>
+        <v/>
+      </c>
+      <c r="H8" s="382">
+        <f>CHOOSE(Scenarios!$D$4,H16,H17,H18)</f>
+        <v/>
+      </c>
+      <c r="I8" s="382">
+        <f>CHOOSE(Scenarios!$D$4,I16,I17,I18)</f>
+        <v/>
+      </c>
+      <c r="J8" s="382">
+        <f>CHOOSE(Scenarios!$D$4,J16,J17,J18)</f>
+        <v/>
+      </c>
+      <c r="K8" s="382">
+        <f>CHOOSE(Scenarios!$D$4,K16,K17,K18)</f>
+        <v/>
+      </c>
+      <c r="L8" s="382">
+        <f>CHOOSE(Scenarios!$D$4,L16,L17,L18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="440" t="inlineStr">
+        <is>
+          <t>Popular volume growth %</t>
+        </is>
+      </c>
+      <c r="E9" s="382">
+        <f>CHOOSE(Scenarios!$D$4,E20,E21,E22)</f>
+        <v/>
+      </c>
+      <c r="F9" s="382">
+        <f>CHOOSE(Scenarios!$D$4,F20,F21,F22)</f>
+        <v/>
+      </c>
+      <c r="G9" s="382">
+        <f>CHOOSE(Scenarios!$D$4,G20,G21,G22)</f>
+        <v/>
+      </c>
+      <c r="H9" s="382">
+        <f>CHOOSE(Scenarios!$D$4,H20,H21,H22)</f>
+        <v/>
+      </c>
+      <c r="I9" s="382">
+        <f>CHOOSE(Scenarios!$D$4,I20,I21,I22)</f>
+        <v/>
+      </c>
+      <c r="J9" s="382">
+        <f>CHOOSE(Scenarios!$D$4,J20,J21,J22)</f>
+        <v/>
+      </c>
+      <c r="K9" s="382">
+        <f>CHOOSE(Scenarios!$D$4,K20,K21,K22)</f>
+        <v/>
+      </c>
+      <c r="L9" s="382">
+        <f>CHOOSE(Scenarios!$D$4,L20,L21,L22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="440" t="inlineStr">
+        <is>
+          <t>Popular price/mix growth %</t>
+        </is>
+      </c>
+      <c r="E10" s="382">
+        <f>CHOOSE(Scenarios!$D$4,E24,E25,E26)</f>
+        <v/>
+      </c>
+      <c r="F10" s="382">
+        <f>CHOOSE(Scenarios!$D$4,F24,F25,F26)</f>
+        <v/>
+      </c>
+      <c r="G10" s="382">
+        <f>CHOOSE(Scenarios!$D$4,G24,G25,G26)</f>
+        <v/>
+      </c>
+      <c r="H10" s="382">
+        <f>CHOOSE(Scenarios!$D$4,H24,H25,H26)</f>
+        <v/>
+      </c>
+      <c r="I10" s="382">
+        <f>CHOOSE(Scenarios!$D$4,I24,I25,I26)</f>
+        <v/>
+      </c>
+      <c r="J10" s="382">
+        <f>CHOOSE(Scenarios!$D$4,J24,J25,J26)</f>
+        <v/>
+      </c>
+      <c r="K10" s="382">
+        <f>CHOOSE(Scenarios!$D$4,K24,K25,K26)</f>
+        <v/>
+      </c>
+      <c r="L10" s="382">
+        <f>CHOOSE(Scenarios!$D$4,L24,L25,L26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="440" t="inlineStr">
+        <is>
+          <t>P&amp;A volume growth %  (Base / Best / Bear)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Base</t>
+        </is>
+      </c>
+      <c r="E12" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F12" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G12" s="382" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="H12" s="382" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I12" s="382" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J12" s="382" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="K12" s="382" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="L12" s="382" t="n">
+        <v>0.028</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Best</t>
+        </is>
+      </c>
+      <c r="E13" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F13" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="382" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H13" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I13" s="382" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="J13" s="382" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="K13" s="382" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="L13" s="382" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bear</t>
+        </is>
+      </c>
+      <c r="E14" s="382" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F14" s="382" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G14" s="382" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="H14" s="382" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I14" s="382" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="J14" s="382" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K14" s="382" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L14" s="382" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="440" t="inlineStr">
+        <is>
+          <t>P&amp;A price/mix growth %  (Base / Best / Bear)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Base</t>
+        </is>
+      </c>
+      <c r="E16" s="382" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F16" s="382" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G16" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H16" s="382" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I16" s="382" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="J16" s="382" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="K16" s="382" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="L16" s="382" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Best</t>
+        </is>
+      </c>
+      <c r="E17" s="382" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F17" s="382" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G17" s="382" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H17" s="382" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I17" s="382" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J17" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K17" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L17" s="382" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bear</t>
+        </is>
+      </c>
+      <c r="E18" s="382" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F18" s="382" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G18" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H18" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I18" s="382" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="J18" s="382" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="K18" s="382" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="L18" s="382" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="440" t="inlineStr">
+        <is>
+          <t>Popular volume growth %  (Base / Best / Bear)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Base</t>
+        </is>
+      </c>
+      <c r="E20" s="382" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F20" s="382" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G20" s="382" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="H20" s="382" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I20" s="382" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="J20" s="382" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="K20" s="382" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L20" s="382" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Best</t>
+        </is>
+      </c>
+      <c r="E21" s="382" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F21" s="382" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G21" s="382" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H21" s="382" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="382" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="382" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="382" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="382" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bear</t>
+        </is>
+      </c>
+      <c r="E22" s="382" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F22" s="382" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G22" s="382" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H22" s="382" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I22" s="382" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J22" s="382" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="K22" s="382" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L22" s="382" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="440" t="inlineStr">
+        <is>
+          <t>Popular price/mix growth %  (Base / Best / Bear)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Base</t>
+        </is>
+      </c>
+      <c r="E24" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F24" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G24" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H24" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I24" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J24" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K24" s="382" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L24" s="382" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Best</t>
+        </is>
+      </c>
+      <c r="E25" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F25" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G25" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H25" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I25" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J25" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K25" s="382" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L25" s="382" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Bear</t>
+        </is>
+      </c>
+      <c r="E26" s="382" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F26" s="382" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G26" s="382" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H26" s="382" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I26" s="382" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J26" s="382" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K26" s="382" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L26" s="382" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="441" t="inlineStr">
+        <is>
+          <t>SEGMENT NET SALES VALUE  (Rs cr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="440" t="inlineStr">
+        <is>
+          <t>P&amp;A NSV</t>
+        </is>
+      </c>
+      <c r="D28" s="259" t="n">
+        <v>11170</v>
+      </c>
+      <c r="E28" s="259">
+        <f>D28*(1+E7)*(1+E8)</f>
+        <v/>
+      </c>
+      <c r="F28" s="259">
+        <f>E28*(1+F7)*(1+F8)</f>
+        <v/>
+      </c>
+      <c r="G28" s="259">
+        <f>F28*(1+G7)*(1+G8)</f>
+        <v/>
+      </c>
+      <c r="H28" s="259">
+        <f>G28*(1+H7)*(1+H8)</f>
+        <v/>
+      </c>
+      <c r="I28" s="259">
+        <f>H28*(1+I7)*(1+I8)</f>
+        <v/>
+      </c>
+      <c r="J28" s="259">
+        <f>I28*(1+J7)*(1+J8)</f>
+        <v/>
+      </c>
+      <c r="K28" s="259">
+        <f>J28*(1+K7)*(1+K8)</f>
+        <v/>
+      </c>
+      <c r="L28" s="259">
+        <f>K28*(1+L7)*(1+L8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="440" t="inlineStr">
+        <is>
+          <t>Popular NSV</t>
+        </is>
+      </c>
+      <c r="D29" s="259" t="n">
+        <v>1122</v>
+      </c>
+      <c r="E29" s="259">
+        <f>D29*(1+E9)*(1+E10)</f>
+        <v/>
+      </c>
+      <c r="F29" s="259">
+        <f>E29*(1+F9)*(1+F10)</f>
+        <v/>
+      </c>
+      <c r="G29" s="259">
+        <f>F29*(1+G9)*(1+G10)</f>
+        <v/>
+      </c>
+      <c r="H29" s="259">
+        <f>G29*(1+H9)*(1+H10)</f>
+        <v/>
+      </c>
+      <c r="I29" s="259">
+        <f>H29*(1+I9)*(1+I10)</f>
+        <v/>
+      </c>
+      <c r="J29" s="259">
+        <f>I29*(1+J9)*(1+J10)</f>
+        <v/>
+      </c>
+      <c r="K29" s="259">
+        <f>J29*(1+K9)*(1+K10)</f>
+        <v/>
+      </c>
+      <c r="L29" s="259">
+        <f>K29*(1+L9)*(1+L10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="440" t="inlineStr">
+        <is>
+          <t>Other NSV (bulk/royalty, held flat)</t>
+        </is>
+      </c>
+      <c r="D30" s="259" t="n">
+        <v>175</v>
+      </c>
+      <c r="E30" s="259">
+        <f>D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="259">
+        <f>E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="259">
+        <f>F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="259">
+        <f>G30</f>
+        <v/>
+      </c>
+      <c r="I30" s="259">
+        <f>H30</f>
+        <v/>
+      </c>
+      <c r="J30" s="259">
+        <f>I30</f>
+        <v/>
+      </c>
+      <c r="K30" s="259">
+        <f>J30</f>
+        <v/>
+      </c>
+      <c r="L30" s="259">
+        <f>K30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="440" t="inlineStr">
+        <is>
+          <t>Total NSV</t>
+        </is>
+      </c>
+      <c r="D31" s="442">
+        <f>SUM(D28:D30)</f>
+        <v/>
+      </c>
+      <c r="E31" s="442">
+        <f>SUM(E28:E30)</f>
+        <v/>
+      </c>
+      <c r="F31" s="442">
+        <f>SUM(F28:F30)</f>
+        <v/>
+      </c>
+      <c r="G31" s="442">
+        <f>SUM(G28:G30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="442">
+        <f>SUM(H28:H30)</f>
+        <v/>
+      </c>
+      <c r="I31" s="442">
+        <f>SUM(I28:I30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="442">
+        <f>SUM(J28:J30)</f>
+        <v/>
+      </c>
+      <c r="K31" s="442">
+        <f>SUM(K28:K30)</f>
+        <v/>
+      </c>
+      <c r="L31" s="442">
+        <f>SUM(L28:L30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="440" t="inlineStr">
+        <is>
+          <t>Blended NSV growth %</t>
+        </is>
+      </c>
+      <c r="E32" s="382">
+        <f>E31/D31-1</f>
+        <v/>
+      </c>
+      <c r="F32" s="382">
+        <f>F31/E31-1</f>
+        <v/>
+      </c>
+      <c r="G32" s="382">
+        <f>G31/F31-1</f>
+        <v/>
+      </c>
+      <c r="H32" s="382">
+        <f>H31/G31-1</f>
+        <v/>
+      </c>
+      <c r="I32" s="382">
+        <f>I31/H31-1</f>
+        <v/>
+      </c>
+      <c r="J32" s="382">
+        <f>J31/I31-1</f>
+        <v/>
+      </c>
+      <c r="K32" s="382">
+        <f>K31/J31-1</f>
+        <v/>
+      </c>
+      <c r="L32" s="382">
+        <f>L31/K31-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="441" t="inlineStr">
+        <is>
+          <t>IMPLIED VOLUME  (mn cases)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="440" t="inlineStr">
+        <is>
+          <t>P&amp;A volume</t>
+        </is>
+      </c>
+      <c r="D34" s="367" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E34" s="367">
+        <f>D34*(1+E7)</f>
+        <v/>
+      </c>
+      <c r="F34" s="367">
+        <f>E34*(1+F7)</f>
+        <v/>
+      </c>
+      <c r="G34" s="367">
+        <f>F34*(1+G7)</f>
+        <v/>
+      </c>
+      <c r="H34" s="367">
+        <f>G34*(1+H7)</f>
+        <v/>
+      </c>
+      <c r="I34" s="367">
+        <f>H34*(1+I7)</f>
+        <v/>
+      </c>
+      <c r="J34" s="367">
+        <f>I34*(1+J7)</f>
+        <v/>
+      </c>
+      <c r="K34" s="367">
+        <f>J34*(1+K7)</f>
+        <v/>
+      </c>
+      <c r="L34" s="367">
+        <f>K34*(1+L7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="440" t="inlineStr">
+        <is>
+          <t>Popular volume</t>
+        </is>
+      </c>
+      <c r="D35" s="367" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E35" s="367">
+        <f>D35*(1+E9)</f>
+        <v/>
+      </c>
+      <c r="F35" s="367">
+        <f>E35*(1+F9)</f>
+        <v/>
+      </c>
+      <c r="G35" s="367">
+        <f>F35*(1+G9)</f>
+        <v/>
+      </c>
+      <c r="H35" s="367">
+        <f>G35*(1+H9)</f>
+        <v/>
+      </c>
+      <c r="I35" s="367">
+        <f>H35*(1+I9)</f>
+        <v/>
+      </c>
+      <c r="J35" s="367">
+        <f>I35*(1+J9)</f>
+        <v/>
+      </c>
+      <c r="K35" s="367">
+        <f>J35*(1+K9)</f>
+        <v/>
+      </c>
+      <c r="L35" s="367">
+        <f>K35*(1+L9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="440" t="inlineStr">
+        <is>
+          <t>Total volume</t>
+        </is>
+      </c>
+      <c r="D36" s="443">
+        <f>SUM(D34:D35)</f>
+        <v/>
+      </c>
+      <c r="E36" s="443">
+        <f>SUM(E34:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="443">
+        <f>SUM(F34:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="443">
+        <f>SUM(G34:G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="443">
+        <f>SUM(H34:H35)</f>
+        <v/>
+      </c>
+      <c r="I36" s="443">
+        <f>SUM(I34:I35)</f>
+        <v/>
+      </c>
+      <c r="J36" s="443">
+        <f>SUM(J34:J35)</f>
+        <v/>
+      </c>
+      <c r="K36" s="443">
+        <f>SUM(K34:K35)</f>
+        <v/>
+      </c>
+      <c r="L36" s="443">
+        <f>SUM(L34:L35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Total volume growth %</t>
+        </is>
+      </c>
+      <c r="E37" s="382">
+        <f>E36/D36-1</f>
+        <v/>
+      </c>
+      <c r="F37" s="382">
+        <f>F36/E36-1</f>
+        <v/>
+      </c>
+      <c r="G37" s="382">
+        <f>G36/F36-1</f>
+        <v/>
+      </c>
+      <c r="H37" s="382">
+        <f>H36/G36-1</f>
+        <v/>
+      </c>
+      <c r="I37" s="382">
+        <f>I36/H36-1</f>
+        <v/>
+      </c>
+      <c r="J37" s="382">
+        <f>J36/I36-1</f>
+        <v/>
+      </c>
+      <c r="K37" s="382">
+        <f>K36/J36-1</f>
+        <v/>
+      </c>
+      <c r="L37" s="382">
+        <f>L36/K36-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="441" t="inlineStr">
+        <is>
+          <t>IMPLIED REALIZATION  (Rs/case, NSV basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="440" t="inlineStr">
+        <is>
+          <t>P&amp;A realization</t>
+        </is>
+      </c>
+      <c r="D39" s="259">
+        <f>D28*10/D34</f>
+        <v/>
+      </c>
+      <c r="E39" s="259">
+        <f>E28*10/E34</f>
+        <v/>
+      </c>
+      <c r="F39" s="259">
+        <f>F28*10/F34</f>
+        <v/>
+      </c>
+      <c r="G39" s="259">
+        <f>G28*10/G34</f>
+        <v/>
+      </c>
+      <c r="H39" s="259">
+        <f>H28*10/H34</f>
+        <v/>
+      </c>
+      <c r="I39" s="259">
+        <f>I28*10/I34</f>
+        <v/>
+      </c>
+      <c r="J39" s="259">
+        <f>J28*10/J34</f>
+        <v/>
+      </c>
+      <c r="K39" s="259">
+        <f>K28*10/K34</f>
+        <v/>
+      </c>
+      <c r="L39" s="259">
+        <f>L28*10/L34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="440" t="inlineStr">
+        <is>
+          <t>Popular realization</t>
+        </is>
+      </c>
+      <c r="D40" s="259">
+        <f>D29*10/D35</f>
+        <v/>
+      </c>
+      <c r="E40" s="259">
+        <f>E29*10/E35</f>
+        <v/>
+      </c>
+      <c r="F40" s="259">
+        <f>F29*10/F35</f>
+        <v/>
+      </c>
+      <c r="G40" s="259">
+        <f>G29*10/G35</f>
+        <v/>
+      </c>
+      <c r="H40" s="259">
+        <f>H29*10/H35</f>
+        <v/>
+      </c>
+      <c r="I40" s="259">
+        <f>I29*10/I35</f>
+        <v/>
+      </c>
+      <c r="J40" s="259">
+        <f>J29*10/J35</f>
+        <v/>
+      </c>
+      <c r="K40" s="259">
+        <f>K29*10/K35</f>
+        <v/>
+      </c>
+      <c r="L40" s="259">
+        <f>L29*10/L35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="441" t="inlineStr">
+        <is>
+          <t>MEMO - NSV salience %</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P&amp;A % of NSV</t>
+        </is>
+      </c>
+      <c r="D43" s="382">
+        <f>D28/D31</f>
+        <v/>
+      </c>
+      <c r="E43" s="382">
+        <f>E28/E31</f>
+        <v/>
+      </c>
+      <c r="F43" s="382">
+        <f>F28/F31</f>
+        <v/>
+      </c>
+      <c r="G43" s="382">
+        <f>G28/G31</f>
+        <v/>
+      </c>
+      <c r="H43" s="382">
+        <f>H28/H31</f>
+        <v/>
+      </c>
+      <c r="I43" s="382">
+        <f>I28/I31</f>
+        <v/>
+      </c>
+      <c r="J43" s="382">
+        <f>J28/J31</f>
+        <v/>
+      </c>
+      <c r="K43" s="382">
+        <f>K28/K31</f>
+        <v/>
+      </c>
+      <c r="L43" s="382">
+        <f>L28/L31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Popular % of NSV</t>
+        </is>
+      </c>
+      <c r="D44" s="382">
+        <f>D29/D31</f>
+        <v/>
+      </c>
+      <c r="E44" s="382">
+        <f>E29/E31</f>
+        <v/>
+      </c>
+      <c r="F44" s="382">
+        <f>F29/F31</f>
+        <v/>
+      </c>
+      <c r="G44" s="382">
+        <f>G29/G31</f>
+        <v/>
+      </c>
+      <c r="H44" s="382">
+        <f>H29/H31</f>
+        <v/>
+      </c>
+      <c r="I44" s="382">
+        <f>I29/I31</f>
+        <v/>
+      </c>
+      <c r="J44" s="382">
+        <f>J29/J31</f>
+        <v/>
+      </c>
+      <c r="K44" s="382">
+        <f>K29/K31</f>
+        <v/>
+      </c>
+      <c r="L44" s="382">
+        <f>L29/L31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Other % of NSV</t>
+        </is>
+      </c>
+      <c r="D45" s="382">
+        <f>D30/D31</f>
+        <v/>
+      </c>
+      <c r="E45" s="382">
+        <f>E30/E31</f>
+        <v/>
+      </c>
+      <c r="F45" s="382">
+        <f>F30/F31</f>
+        <v/>
+      </c>
+      <c r="G45" s="382">
+        <f>G30/G31</f>
+        <v/>
+      </c>
+      <c r="H45" s="382">
+        <f>H30/H31</f>
+        <v/>
+      </c>
+      <c r="I45" s="382">
+        <f>I30/I31</f>
+        <v/>
+      </c>
+      <c r="J45" s="382">
+        <f>J30/J31</f>
+        <v/>
+      </c>
+      <c r="K45" s="382">
+        <f>K30/K31</f>
+        <v/>
+      </c>
+      <c r="L45" s="382">
+        <f>L30/L31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="440" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; METHOD:</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FY26 base NSV split from FY2026 Integrated Annual Report MD&amp;A: P&amp;A 89.6%, Popular 9.0%, Other (bulk/royalty) ~1.4% of NSV Rs12,467cr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FY26 volume ~65mn cases (+1.5% YoY per AR); P&amp;A ~55.2mn / Popular ~9.8mn reconstructed from FY25 (P&amp;A 53.12mn, Popular 10.88mn) + AR FY26 segment growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>P&amp;A growth algorithm (Q2-Q4 FY26 concalls, Praveen Someshwar/Pradeep Jain): '4-5% volume/mix + 6-8% price/mix = double-digit P&amp;A growth'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Base case calibrated so blended NSV growth (~9% FY27 fading to ~6.7%) reconciles to the model's prior Scenarios base path; Best reflects the full double-digit P&amp;A algorithm; Bear is a volume-led downturn with continued Popular decline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Popular segment: management is deliberately exiting low-margin Popular (NSV -0.3% FY26); modeled as continued volume decline offset by price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Other NSV (bulk scotch / franchise / royalty) held flat absent specific guidance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19887,7 +22614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21536,7 +24263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25439,7 +28166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26436,7 +29163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28427,7 +31154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28578,35 +31305,35 @@
         <v>12467</v>
       </c>
       <c r="M5" s="355">
-        <f>L5*(1+Scenarios!H10)</f>
+        <f>'Revenue Drivers'!E31</f>
         <v/>
       </c>
       <c r="N5" s="355">
-        <f>M5*(1+Scenarios!I10)</f>
+        <f>'Revenue Drivers'!F31</f>
         <v/>
       </c>
       <c r="O5" s="355">
-        <f>N5*(1+Scenarios!J10)</f>
+        <f>'Revenue Drivers'!G31</f>
         <v/>
       </c>
       <c r="P5" s="355">
-        <f>O5*(1+Scenarios!K10)</f>
+        <f>'Revenue Drivers'!H31</f>
         <v/>
       </c>
       <c r="Q5" s="355">
-        <f>P5*(1+Scenarios!L10)</f>
+        <f>'Revenue Drivers'!I31</f>
         <v/>
       </c>
       <c r="R5" s="355">
-        <f>Q5*(1+Scenarios!M10)</f>
+        <f>'Revenue Drivers'!J31</f>
         <v/>
       </c>
       <c r="S5" s="355">
-        <f>R5*(1+Scenarios!N10)</f>
+        <f>'Revenue Drivers'!K31</f>
         <v/>
       </c>
       <c r="T5" s="355">
-        <f>S5*(1+Scenarios!O10)</f>
+        <f>'Revenue Drivers'!L31</f>
         <v/>
       </c>
     </row>
@@ -29843,7 +32570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32143,1386 +34870,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A2:T29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18" customHeight="1"/>
-  <cols>
-    <col width="2.77734375" customWidth="1" min="1" max="1"/>
-    <col width="50.77734375" customWidth="1" min="2" max="2"/>
-    <col width="10.77734375" customWidth="1" style="335" min="3" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1"/>
-    <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="45" t="inlineStr">
-        <is>
-          <t>Cash Flow Statement</t>
-        </is>
-      </c>
-      <c r="T2" s="246">
-        <f>BS!T2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Particulars</t>
-        </is>
-      </c>
-      <c r="C4" s="375" t="n">
-        <v>2017</v>
-      </c>
-      <c r="D4" s="375">
-        <f>C4+1</f>
-        <v/>
-      </c>
-      <c r="E4" s="375">
-        <f>D4+1</f>
-        <v/>
-      </c>
-      <c r="F4" s="375">
-        <f>E4+1</f>
-        <v/>
-      </c>
-      <c r="G4" s="375">
-        <f>F4+1</f>
-        <v/>
-      </c>
-      <c r="H4" s="375">
-        <f>G4+1</f>
-        <v/>
-      </c>
-      <c r="I4" s="375">
-        <f>H4+1</f>
-        <v/>
-      </c>
-      <c r="J4" s="375">
-        <f>I4+1</f>
-        <v/>
-      </c>
-      <c r="K4" s="375">
-        <f>J4+1</f>
-        <v/>
-      </c>
-      <c r="L4" s="375">
-        <f>K4+1</f>
-        <v/>
-      </c>
-      <c r="M4" s="376">
-        <f>L4+1</f>
-        <v/>
-      </c>
-      <c r="N4" s="376">
-        <f>M4+1</f>
-        <v/>
-      </c>
-      <c r="O4" s="376">
-        <f>N4+1</f>
-        <v/>
-      </c>
-      <c r="P4" s="376">
-        <f>O4+1</f>
-        <v/>
-      </c>
-      <c r="Q4" s="376">
-        <f>P4+1</f>
-        <v/>
-      </c>
-      <c r="R4" s="376">
-        <f>Q4+1</f>
-        <v/>
-      </c>
-      <c r="S4" s="376">
-        <f>R4+1</f>
-        <v/>
-      </c>
-      <c r="T4" s="376">
-        <f>S4+1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1"/>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Net Profit Aafter Tax (PAT)</t>
-        </is>
-      </c>
-      <c r="C6" s="388">
-        <f>PL!C22</f>
-        <v/>
-      </c>
-      <c r="D6" s="388">
-        <f>PL!D22</f>
-        <v/>
-      </c>
-      <c r="E6" s="388">
-        <f>PL!E22</f>
-        <v/>
-      </c>
-      <c r="F6" s="388">
-        <f>PL!F22</f>
-        <v/>
-      </c>
-      <c r="G6" s="388">
-        <f>PL!G22</f>
-        <v/>
-      </c>
-      <c r="H6" s="388">
-        <f>PL!H22</f>
-        <v/>
-      </c>
-      <c r="I6" s="388">
-        <f>PL!I22</f>
-        <v/>
-      </c>
-      <c r="J6" s="388">
-        <f>PL!J22</f>
-        <v/>
-      </c>
-      <c r="K6" s="388">
-        <f>PL!K22</f>
-        <v/>
-      </c>
-      <c r="L6" s="388">
-        <f>PL!L22</f>
-        <v/>
-      </c>
-      <c r="M6" s="388">
-        <f>PL!M22</f>
-        <v/>
-      </c>
-      <c r="N6" s="388">
-        <f>PL!N22</f>
-        <v/>
-      </c>
-      <c r="O6" s="388">
-        <f>PL!O22</f>
-        <v/>
-      </c>
-      <c r="P6" s="388">
-        <f>PL!P22</f>
-        <v/>
-      </c>
-      <c r="Q6" s="388">
-        <f>PL!Q22</f>
-        <v/>
-      </c>
-      <c r="R6" s="388">
-        <f>PL!R22</f>
-        <v/>
-      </c>
-      <c r="S6" s="388">
-        <f>PL!S22</f>
-        <v/>
-      </c>
-      <c r="T6" s="388">
-        <f>PL!T22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="C7" s="353">
-        <f>-PL!C13</f>
-        <v/>
-      </c>
-      <c r="D7" s="353">
-        <f>-PL!D13</f>
-        <v/>
-      </c>
-      <c r="E7" s="353">
-        <f>-PL!E13</f>
-        <v/>
-      </c>
-      <c r="F7" s="353">
-        <f>-PL!F13</f>
-        <v/>
-      </c>
-      <c r="G7" s="353">
-        <f>-PL!G13</f>
-        <v/>
-      </c>
-      <c r="H7" s="353">
-        <f>-PL!H13</f>
-        <v/>
-      </c>
-      <c r="I7" s="353">
-        <f>-PL!I13</f>
-        <v/>
-      </c>
-      <c r="J7" s="353">
-        <f>-PL!J13</f>
-        <v/>
-      </c>
-      <c r="K7" s="353">
-        <f>-PL!K13</f>
-        <v/>
-      </c>
-      <c r="L7" s="353">
-        <f>-PL!L13</f>
-        <v/>
-      </c>
-      <c r="M7" s="353">
-        <f>-PL!M13</f>
-        <v/>
-      </c>
-      <c r="N7" s="353">
-        <f>-PL!N13</f>
-        <v/>
-      </c>
-      <c r="O7" s="353">
-        <f>-PL!O13</f>
-        <v/>
-      </c>
-      <c r="P7" s="353">
-        <f>-PL!P13</f>
-        <v/>
-      </c>
-      <c r="Q7" s="353">
-        <f>-PL!Q13</f>
-        <v/>
-      </c>
-      <c r="R7" s="353">
-        <f>-PL!R13</f>
-        <v/>
-      </c>
-      <c r="S7" s="353">
-        <f>-PL!S13</f>
-        <v/>
-      </c>
-      <c r="T7" s="353">
-        <f>-PL!T13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="96" t="inlineStr">
-        <is>
-          <t>+/- in other non cash items</t>
-        </is>
-      </c>
-      <c r="C8" s="380" t="n">
-        <v>227.2</v>
-      </c>
-      <c r="D8" s="380" t="n">
-        <v>358.900000000002</v>
-      </c>
-      <c r="E8" s="380" t="n">
-        <v>103.8999999999987</v>
-      </c>
-      <c r="F8" s="380" t="n">
-        <v>3.000000000000853</v>
-      </c>
-      <c r="G8" s="380" t="n">
-        <v>1752.2</v>
-      </c>
-      <c r="H8" s="380" t="n">
-        <v>611.5000000000007</v>
-      </c>
-      <c r="I8" s="380" t="n">
-        <v>-468.8000000000003</v>
-      </c>
-      <c r="J8" s="380" t="n">
-        <v>-431.8999999999996</v>
-      </c>
-      <c r="K8" s="380" t="n">
-        <v>94.59999999999991</v>
-      </c>
-      <c r="L8" s="380" t="n">
-        <v>-37</v>
-      </c>
-      <c r="M8" s="335">
-        <f>-PL!M18-PL!M17</f>
-        <v/>
-      </c>
-      <c r="N8" s="335">
-        <f>-PL!N18-PL!N17</f>
-        <v/>
-      </c>
-      <c r="O8" s="335">
-        <f>-PL!O18-PL!O17</f>
-        <v/>
-      </c>
-      <c r="P8" s="335">
-        <f>-PL!P18-PL!P17</f>
-        <v/>
-      </c>
-      <c r="Q8" s="335">
-        <f>-PL!Q18-PL!Q17</f>
-        <v/>
-      </c>
-      <c r="R8" s="335">
-        <f>-PL!R18-PL!R17</f>
-        <v/>
-      </c>
-      <c r="S8" s="335">
-        <f>-PL!S18-PL!S17</f>
-        <v/>
-      </c>
-      <c r="T8" s="335">
-        <f>-PL!T18-PL!T17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="153" t="inlineStr">
-        <is>
-          <t>+/- change in NWC</t>
-        </is>
-      </c>
-      <c r="C9" s="389" t="n">
-        <v>138</v>
-      </c>
-      <c r="D9" s="390">
-        <f>-'Working Capital Schedule'!D21</f>
-        <v/>
-      </c>
-      <c r="E9" s="390">
-        <f>-'Working Capital Schedule'!E21</f>
-        <v/>
-      </c>
-      <c r="F9" s="390">
-        <f>-'Working Capital Schedule'!F21</f>
-        <v/>
-      </c>
-      <c r="G9" s="390">
-        <f>-'Working Capital Schedule'!G21</f>
-        <v/>
-      </c>
-      <c r="H9" s="390">
-        <f>-'Working Capital Schedule'!H21</f>
-        <v/>
-      </c>
-      <c r="I9" s="390">
-        <f>-'Working Capital Schedule'!I21</f>
-        <v/>
-      </c>
-      <c r="J9" s="390">
-        <f>-'Working Capital Schedule'!J21</f>
-        <v/>
-      </c>
-      <c r="K9" s="390">
-        <f>-'Working Capital Schedule'!K21</f>
-        <v/>
-      </c>
-      <c r="L9" s="390">
-        <f>-'Working Capital Schedule'!L21</f>
-        <v/>
-      </c>
-      <c r="M9" s="390">
-        <f>-'Working Capital Schedule'!M21</f>
-        <v/>
-      </c>
-      <c r="N9" s="390">
-        <f>-'Working Capital Schedule'!N21</f>
-        <v/>
-      </c>
-      <c r="O9" s="390">
-        <f>-'Working Capital Schedule'!O21</f>
-        <v/>
-      </c>
-      <c r="P9" s="390">
-        <f>-'Working Capital Schedule'!P21</f>
-        <v/>
-      </c>
-      <c r="Q9" s="390">
-        <f>-'Working Capital Schedule'!Q21</f>
-        <v/>
-      </c>
-      <c r="R9" s="390">
-        <f>-'Working Capital Schedule'!R21</f>
-        <v/>
-      </c>
-      <c r="S9" s="390">
-        <f>-'Working Capital Schedule'!S21</f>
-        <v/>
-      </c>
-      <c r="T9" s="390">
-        <f>-'Working Capital Schedule'!T21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>Cash flow from Operating Activities</t>
-        </is>
-      </c>
-      <c r="C10" s="355">
-        <f>SUM(C6:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="355">
-        <f>SUM(D6:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="355">
-        <f>SUM(E6:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="355">
-        <f>SUM(F6:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="355">
-        <f>SUM(G6:G9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="355">
-        <f>SUM(H6:H9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="355">
-        <f>SUM(I6:I9)</f>
-        <v/>
-      </c>
-      <c r="J10" s="355">
-        <f>SUM(J6:J9)</f>
-        <v/>
-      </c>
-      <c r="K10" s="355">
-        <f>SUM(K6:K9)</f>
-        <v/>
-      </c>
-      <c r="L10" s="355">
-        <f>SUM(L6:L9)</f>
-        <v/>
-      </c>
-      <c r="M10" s="355">
-        <f>SUM(M6:M9)</f>
-        <v/>
-      </c>
-      <c r="N10" s="355">
-        <f>SUM(N6:N9)</f>
-        <v/>
-      </c>
-      <c r="O10" s="355">
-        <f>SUM(O6:O9)</f>
-        <v/>
-      </c>
-      <c r="P10" s="355">
-        <f>SUM(P6:P9)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="355">
-        <f>SUM(Q6:Q9)</f>
-        <v/>
-      </c>
-      <c r="R10" s="355">
-        <f>SUM(R6:R9)</f>
-        <v/>
-      </c>
-      <c r="S10" s="355">
-        <f>SUM(S6:S9)</f>
-        <v/>
-      </c>
-      <c r="T10" s="355">
-        <f>SUM(T6:T9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Interest Received</t>
-        </is>
-      </c>
-      <c r="C11" s="335" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="D11" s="335" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E11" s="335" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F11" s="335" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G11" s="335" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H11" s="335" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I11" s="335" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="J11" s="335" t="n">
-        <v>42</v>
-      </c>
-      <c r="K11" s="335" t="n">
-        <v>36</v>
-      </c>
-      <c r="L11" s="335" t="n">
-        <v>67</v>
-      </c>
-      <c r="M11" s="335">
-        <f>M21*Assumptions!E9</f>
-        <v/>
-      </c>
-      <c r="N11" s="335">
-        <f>N21*Assumptions!F9</f>
-        <v/>
-      </c>
-      <c r="O11" s="335">
-        <f>O21*Assumptions!G9</f>
-        <v/>
-      </c>
-      <c r="P11" s="335">
-        <f>P21*Assumptions!H9</f>
-        <v/>
-      </c>
-      <c r="Q11" s="335">
-        <f>Q21*Assumptions!I9</f>
-        <v/>
-      </c>
-      <c r="R11" s="335">
-        <f>R21*Assumptions!J9</f>
-        <v/>
-      </c>
-      <c r="S11" s="335">
-        <f>S21*Assumptions!K9</f>
-        <v/>
-      </c>
-      <c r="T11" s="335">
-        <f>T21*Assumptions!L9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Capex</t>
-        </is>
-      </c>
-      <c r="C12" s="335" t="n">
-        <v>-311</v>
-      </c>
-      <c r="D12" s="335" t="n">
-        <v>-184.3</v>
-      </c>
-      <c r="E12" s="335" t="n">
-        <v>-173</v>
-      </c>
-      <c r="F12" s="335" t="n">
-        <v>-211.6</v>
-      </c>
-      <c r="G12" s="335" t="n">
-        <v>-158.9</v>
-      </c>
-      <c r="H12" s="335" t="n">
-        <v>-134</v>
-      </c>
-      <c r="I12" s="335" t="n">
-        <v>-136.6</v>
-      </c>
-      <c r="J12" s="335" t="n">
-        <v>-98</v>
-      </c>
-      <c r="K12" s="335" t="n">
-        <v>-162</v>
-      </c>
-      <c r="L12" s="335" t="n">
-        <v>-181</v>
-      </c>
-      <c r="M12" s="335">
-        <f>-'Working Schedules'!H42</f>
-        <v/>
-      </c>
-      <c r="N12" s="335">
-        <f>-'Working Schedules'!I42</f>
-        <v/>
-      </c>
-      <c r="O12" s="335">
-        <f>-'Working Schedules'!J42</f>
-        <v/>
-      </c>
-      <c r="P12" s="335">
-        <f>-'Working Schedules'!K42</f>
-        <v/>
-      </c>
-      <c r="Q12" s="335">
-        <f>-'Working Schedules'!L42</f>
-        <v/>
-      </c>
-      <c r="R12" s="335">
-        <f>-'Working Schedules'!M42</f>
-        <v/>
-      </c>
-      <c r="S12" s="335">
-        <f>-'Working Schedules'!N42</f>
-        <v/>
-      </c>
-      <c r="T12" s="335">
-        <f>-'Working Schedules'!O42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="151" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="C13" s="391" t="n">
-        <v>64</v>
-      </c>
-      <c r="D13" s="391" t="n">
-        <v>284</v>
-      </c>
-      <c r="E13" s="391" t="n">
-        <v>128</v>
-      </c>
-      <c r="F13" s="391" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" s="391" t="n">
-        <v>35</v>
-      </c>
-      <c r="H13" s="391" t="n">
-        <v>-176</v>
-      </c>
-      <c r="I13" s="391" t="n">
-        <v>12</v>
-      </c>
-      <c r="J13" s="391" t="n">
-        <v>-262</v>
-      </c>
-      <c r="K13" s="391" t="n">
-        <v>-227</v>
-      </c>
-      <c r="L13" s="391" t="n">
-        <v>75</v>
-      </c>
-      <c r="M13" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="391" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>Cash flow from investing activities</t>
-        </is>
-      </c>
-      <c r="C14" s="355">
-        <f>SUM(C11:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="355">
-        <f>SUM(D11:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="355">
-        <f>SUM(E11:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="355">
-        <f>SUM(F11:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="355">
-        <f>SUM(G11:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="355">
-        <f>SUM(H11:H13)</f>
-        <v/>
-      </c>
-      <c r="I14" s="355">
-        <f>SUM(I11:I13)</f>
-        <v/>
-      </c>
-      <c r="J14" s="355">
-        <f>SUM(J11:J13)</f>
-        <v/>
-      </c>
-      <c r="K14" s="355">
-        <f>SUM(K11:K13)</f>
-        <v/>
-      </c>
-      <c r="L14" s="355">
-        <f>SUM(L11:L13)</f>
-        <v/>
-      </c>
-      <c r="M14" s="355">
-        <f>SUM(M11:M13)</f>
-        <v/>
-      </c>
-      <c r="N14" s="355">
-        <f>SUM(N11:N13)</f>
-        <v/>
-      </c>
-      <c r="O14" s="355">
-        <f>SUM(O11:O13)</f>
-        <v/>
-      </c>
-      <c r="P14" s="355">
-        <f>SUM(P11:P13)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="355">
-        <f>SUM(Q11:Q13)</f>
-        <v/>
-      </c>
-      <c r="R14" s="355">
-        <f>SUM(R11:R13)</f>
-        <v/>
-      </c>
-      <c r="S14" s="355">
-        <f>SUM(S11:S13)</f>
-        <v/>
-      </c>
-      <c r="T14" s="355">
-        <f>SUM(T11:T13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Repayment Lease Liabilities</t>
-        </is>
-      </c>
-      <c r="C15" s="335" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="D15" s="335" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="335" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="335" t="n">
-        <v>-64.5</v>
-      </c>
-      <c r="G15" s="335" t="n">
-        <v>-80.7</v>
-      </c>
-      <c r="H15" s="335" t="n">
-        <v>-100.2</v>
-      </c>
-      <c r="I15" s="335" t="n">
-        <v>-124</v>
-      </c>
-      <c r="J15" s="335" t="n">
-        <v>-126</v>
-      </c>
-      <c r="K15" s="335" t="n">
-        <v>-137</v>
-      </c>
-      <c r="L15" s="335" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M15" s="335">
-        <f>'Working Schedules'!H9</f>
-        <v/>
-      </c>
-      <c r="N15" s="335">
-        <f>'Working Schedules'!I9</f>
-        <v/>
-      </c>
-      <c r="O15" s="335">
-        <f>'Working Schedules'!J9</f>
-        <v/>
-      </c>
-      <c r="P15" s="335">
-        <f>'Working Schedules'!K9</f>
-        <v/>
-      </c>
-      <c r="Q15" s="335">
-        <f>'Working Schedules'!L9</f>
-        <v/>
-      </c>
-      <c r="R15" s="335">
-        <f>'Working Schedules'!M9</f>
-        <v/>
-      </c>
-      <c r="S15" s="335">
-        <f>'Working Schedules'!N9</f>
-        <v/>
-      </c>
-      <c r="T15" s="335">
-        <f>'Working Schedules'!O9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Interest Paid</t>
-        </is>
-      </c>
-      <c r="C16" s="335" t="n">
-        <v>-375.2</v>
-      </c>
-      <c r="D16" s="335" t="n">
-        <v>-252.8</v>
-      </c>
-      <c r="E16" s="335" t="n">
-        <v>-229.3</v>
-      </c>
-      <c r="F16" s="335" t="n">
-        <v>-181.1</v>
-      </c>
-      <c r="G16" s="335" t="n">
-        <v>-142</v>
-      </c>
-      <c r="H16" s="335" t="n">
-        <v>-50.1</v>
-      </c>
-      <c r="I16" s="335" t="n">
-        <v>-36.3</v>
-      </c>
-      <c r="J16" s="335" t="n">
-        <v>-21</v>
-      </c>
-      <c r="K16" s="335" t="n">
-        <v>-40</v>
-      </c>
-      <c r="L16" s="335" t="n">
-        <v>-37</v>
-      </c>
-      <c r="M16" s="335">
-        <f>PL!M17</f>
-        <v/>
-      </c>
-      <c r="N16" s="335">
-        <f>PL!N17</f>
-        <v/>
-      </c>
-      <c r="O16" s="335">
-        <f>PL!O17</f>
-        <v/>
-      </c>
-      <c r="P16" s="335">
-        <f>PL!P17</f>
-        <v/>
-      </c>
-      <c r="Q16" s="335">
-        <f>PL!Q17</f>
-        <v/>
-      </c>
-      <c r="R16" s="335">
-        <f>PL!R17</f>
-        <v/>
-      </c>
-      <c r="S16" s="335">
-        <f>PL!S17</f>
-        <v/>
-      </c>
-      <c r="T16" s="335">
-        <f>PL!T17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Dividend Paid</t>
-        </is>
-      </c>
-      <c r="C17" s="335" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="335" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="335" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="335" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="335" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="335" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="335" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="335" t="n">
-        <v>-284</v>
-      </c>
-      <c r="K17" s="335" t="n">
-        <v>-355</v>
-      </c>
-      <c r="L17" s="335" t="n">
-        <v>-1263</v>
-      </c>
-      <c r="M17" s="335">
-        <f>-Assumptions!E11*PL!M22</f>
-        <v/>
-      </c>
-      <c r="N17" s="335">
-        <f>-Assumptions!F11*PL!N22</f>
-        <v/>
-      </c>
-      <c r="O17" s="335">
-        <f>-Assumptions!G11*PL!O22</f>
-        <v/>
-      </c>
-      <c r="P17" s="335">
-        <f>-Assumptions!H11*PL!P22</f>
-        <v/>
-      </c>
-      <c r="Q17" s="335">
-        <f>-Assumptions!I11*PL!Q22</f>
-        <v/>
-      </c>
-      <c r="R17" s="335">
-        <f>-Assumptions!J11*PL!R22</f>
-        <v/>
-      </c>
-      <c r="S17" s="335">
-        <f>-Assumptions!K11*PL!S22</f>
-        <v/>
-      </c>
-      <c r="T17" s="335">
-        <f>-Assumptions!L11*PL!T22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="151" t="inlineStr">
-        <is>
-          <t>Others</t>
-        </is>
-      </c>
-      <c r="C18" s="391" t="n">
-        <v>-86.40000000000001</v>
-      </c>
-      <c r="D18" s="391" t="n">
-        <v>-607.4</v>
-      </c>
-      <c r="E18" s="391" t="n">
-        <v>-653.6000000000003</v>
-      </c>
-      <c r="F18" s="391" t="n">
-        <v>-553.6</v>
-      </c>
-      <c r="G18" s="391" t="n">
-        <v>-1471.800000000001</v>
-      </c>
-      <c r="H18" s="391" t="n">
-        <v>-324.9</v>
-      </c>
-      <c r="I18" s="391" t="n">
-        <v>505.9</v>
-      </c>
-      <c r="J18" s="391" t="n">
-        <v>359.9</v>
-      </c>
-      <c r="K18" s="391" t="n">
-        <v>-27</v>
-      </c>
-      <c r="L18" s="391" t="n">
-        <v>255</v>
-      </c>
-      <c r="M18" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="391" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="391" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>Cash flow from Financing activities</t>
-        </is>
-      </c>
-      <c r="C19" s="355">
-        <f>SUM(C15:C18)</f>
-        <v/>
-      </c>
-      <c r="D19" s="355">
-        <f>SUM(D15:D18)</f>
-        <v/>
-      </c>
-      <c r="E19" s="355">
-        <f>SUM(E15:E18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="355">
-        <f>SUM(F15:F18)</f>
-        <v/>
-      </c>
-      <c r="G19" s="355">
-        <f>SUM(G15:G18)</f>
-        <v/>
-      </c>
-      <c r="H19" s="355">
-        <f>SUM(H15:H18)</f>
-        <v/>
-      </c>
-      <c r="I19" s="355">
-        <f>SUM(I15:I18)</f>
-        <v/>
-      </c>
-      <c r="J19" s="355">
-        <f>SUM(J15:J18)</f>
-        <v/>
-      </c>
-      <c r="K19" s="355">
-        <f>SUM(K15:K18)</f>
-        <v/>
-      </c>
-      <c r="L19" s="355">
-        <f>SUM(L15:L18)</f>
-        <v/>
-      </c>
-      <c r="M19" s="355">
-        <f>SUM(M15:M18)</f>
-        <v/>
-      </c>
-      <c r="N19" s="355">
-        <f>SUM(N15:N18)</f>
-        <v/>
-      </c>
-      <c r="O19" s="355">
-        <f>SUM(O15:O18)</f>
-        <v/>
-      </c>
-      <c r="P19" s="355">
-        <f>SUM(P15:P18)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="355">
-        <f>SUM(Q15:Q18)</f>
-        <v/>
-      </c>
-      <c r="R19" s="355">
-        <f>SUM(R15:R18)</f>
-        <v/>
-      </c>
-      <c r="S19" s="355">
-        <f>SUM(S15:S18)</f>
-        <v/>
-      </c>
-      <c r="T19" s="355">
-        <f>SUM(T15:T18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>Net change in Cash</t>
-        </is>
-      </c>
-      <c r="C20" s="355">
-        <f>C10+C14+C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="355">
-        <f>D10+D14+D19</f>
-        <v/>
-      </c>
-      <c r="E20" s="355">
-        <f>E10+E14+E19</f>
-        <v/>
-      </c>
-      <c r="F20" s="355">
-        <f>F10+F14+F19</f>
-        <v/>
-      </c>
-      <c r="G20" s="355">
-        <f>G10+G14+G19</f>
-        <v/>
-      </c>
-      <c r="H20" s="355">
-        <f>H10+H14+H19</f>
-        <v/>
-      </c>
-      <c r="I20" s="355">
-        <f>I10+I14+I19</f>
-        <v/>
-      </c>
-      <c r="J20" s="355">
-        <f>J10+J14+J19</f>
-        <v/>
-      </c>
-      <c r="K20" s="355">
-        <f>K10+K14+K19</f>
-        <v/>
-      </c>
-      <c r="L20" s="355">
-        <f>L10+L14+L19</f>
-        <v/>
-      </c>
-      <c r="M20" s="355">
-        <f>M10+M14+M19</f>
-        <v/>
-      </c>
-      <c r="N20" s="355">
-        <f>N10+N14+N19</f>
-        <v/>
-      </c>
-      <c r="O20" s="355">
-        <f>O10+O14+O19</f>
-        <v/>
-      </c>
-      <c r="P20" s="355">
-        <f>P10+P14+P19</f>
-        <v/>
-      </c>
-      <c r="Q20" s="355">
-        <f>Q10+Q14+Q19</f>
-        <v/>
-      </c>
-      <c r="R20" s="355">
-        <f>R10+R14+R19</f>
-        <v/>
-      </c>
-      <c r="S20" s="355">
-        <f>S10+S14+S19</f>
-        <v/>
-      </c>
-      <c r="T20" s="355">
-        <f>T10+T14+T19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="151" t="inlineStr">
-        <is>
-          <t>Opening Cash Balance</t>
-        </is>
-      </c>
-      <c r="C21" s="389" t="n">
-        <v>138</v>
-      </c>
-      <c r="D21" s="390">
-        <f>C22</f>
-        <v/>
-      </c>
-      <c r="E21" s="390">
-        <f>D22</f>
-        <v/>
-      </c>
-      <c r="F21" s="390">
-        <f>E22</f>
-        <v/>
-      </c>
-      <c r="G21" s="390">
-        <f>F22</f>
-        <v/>
-      </c>
-      <c r="H21" s="390">
-        <f>G22</f>
-        <v/>
-      </c>
-      <c r="I21" s="390">
-        <f>H22</f>
-        <v/>
-      </c>
-      <c r="J21" s="390">
-        <f>I22</f>
-        <v/>
-      </c>
-      <c r="K21" s="390">
-        <f>J22</f>
-        <v/>
-      </c>
-      <c r="L21" s="390">
-        <f>K22</f>
-        <v/>
-      </c>
-      <c r="M21" s="390">
-        <f>L22</f>
-        <v/>
-      </c>
-      <c r="N21" s="390">
-        <f>M22</f>
-        <v/>
-      </c>
-      <c r="O21" s="390">
-        <f>N22</f>
-        <v/>
-      </c>
-      <c r="P21" s="390">
-        <f>O22</f>
-        <v/>
-      </c>
-      <c r="Q21" s="390">
-        <f>P22</f>
-        <v/>
-      </c>
-      <c r="R21" s="390">
-        <f>Q22</f>
-        <v/>
-      </c>
-      <c r="S21" s="390">
-        <f>R22</f>
-        <v/>
-      </c>
-      <c r="T21" s="390">
-        <f>S22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>Closing Cash Balance</t>
-        </is>
-      </c>
-      <c r="C22" s="355">
-        <f>C20+C21</f>
-        <v/>
-      </c>
-      <c r="D22" s="355">
-        <f>D20+D21</f>
-        <v/>
-      </c>
-      <c r="E22" s="355">
-        <f>E20+E21</f>
-        <v/>
-      </c>
-      <c r="F22" s="355">
-        <f>F20+F21</f>
-        <v/>
-      </c>
-      <c r="G22" s="355">
-        <f>G20+G21</f>
-        <v/>
-      </c>
-      <c r="H22" s="355">
-        <f>H20+H21</f>
-        <v/>
-      </c>
-      <c r="I22" s="355">
-        <f>I20+I21</f>
-        <v/>
-      </c>
-      <c r="J22" s="355">
-        <f>J20+J21</f>
-        <v/>
-      </c>
-      <c r="K22" s="355">
-        <f>K20+K21</f>
-        <v/>
-      </c>
-      <c r="L22" s="355">
-        <f>L20+L21</f>
-        <v/>
-      </c>
-      <c r="M22" s="355">
-        <f>M20+M21</f>
-        <v/>
-      </c>
-      <c r="N22" s="355">
-        <f>N20+N21</f>
-        <v/>
-      </c>
-      <c r="O22" s="355">
-        <f>O20+O21</f>
-        <v/>
-      </c>
-      <c r="P22" s="355">
-        <f>P20+P21</f>
-        <v/>
-      </c>
-      <c r="Q22" s="355">
-        <f>Q20+Q21</f>
-        <v/>
-      </c>
-      <c r="R22" s="355">
-        <f>R20+R21</f>
-        <v/>
-      </c>
-      <c r="S22" s="355">
-        <f>S20+S21</f>
-        <v/>
-      </c>
-      <c r="T22" s="355">
-        <f>T20+T21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="96" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="96" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>